--- a/mixs-templates/Misag_plus_combinations/MisagSoil.xlsx
+++ b/mixs-templates/Misag_plus_combinations/MisagSoil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ1"/>
+  <dimension ref="A1:DM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,382 +614,397 @@
       </c>
       <c r="AN1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>sort_tech</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>wga_amp_appr</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>sc_lysis_approach</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>cur_land_use</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>cur_vegetation</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>cur_vegetation_meth</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>previous_land_use</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>prev_land_use_meth</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>crop_rotation</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>agrochem_addition</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>tillage</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>flooding</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>extreme_event</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>soil_horizon</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>horizon_meth</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>sieving</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>water_content</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>water_cont_soil_meth</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>pool_dna_extracts</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>store_cond</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>link_climate_info</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>annual_temp</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>season_temp</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>annual_precpt</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>season_precpt</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>link_class_info</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>fao_class</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>local_class</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>local_class_meth</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>org_nitro</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>soil_type</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>soil_type_meth</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>slope_gradient</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>slope_aspect</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>profile_position</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>drainage_class</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>soil_texture</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>soil_texture_meth</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>ph_meth</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>org_matter</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>tot_org_carb</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>tot_org_c_meth</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>tot_nitro_content</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>tot_nitro_cont_meth</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>microbial_biomass</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>micro_biomass_meth</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>link_addit_analys</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>heavy_metals</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>heavy_metals_meth</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>al_sat</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>al_sat_meth</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>misc_param</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>season</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="14">
+  <dataValidations count="15">
     <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"contigs,reads"</formula1>
     </dataValidation>
@@ -1008,29 +1023,32 @@
     <dataValidation sqref="AI2:AI1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AT2:AT1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"flow cytometric cell sorting,lazer-tweezing,microfluidics,micromanipulation,optical manipulation,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AY2:AY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"mda based,pcr based"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="BB2:BB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BD2:BD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"chemical,combination,enzymatic,physical"</formula1>
     </dataValidation>
-    <dataValidation sqref="BS2:BS1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BU2:BU1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"chisel,cutting disc,disc plough,drill,mouldboard,ridge till,strip tillage,tined,zonal tillage"</formula1>
     </dataValidation>
-    <dataValidation sqref="BW2:BW1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BY2:BY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A horizon,B horizon,C horizon,E horizon,O horizon,Permafrost,R layer"</formula1>
     </dataValidation>
-    <dataValidation sqref="CR2:CR1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CT2:CT1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"backslope,footslope,shoulder,summit,toeslope"</formula1>
     </dataValidation>
-    <dataValidation sqref="CS2:CS1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CU2:CU1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"excessively drained,moderately well,poorly,somewhat poorly,very poorly,well"</formula1>
+    </dataValidation>
+    <dataValidation sqref="DM2:DM1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"autumn [NCIT:C94733],spring [NCIT:C94731],summer [NCIT:C94732],winter [NCIT:C94730]"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
